--- a/data/trans_camb/P5B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 0,19</t>
+          <t>-11,3; 0,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 3,45</t>
+          <t>-9,31; 3,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 0,99</t>
+          <t>-11,17; 1,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 1,43</t>
+          <t>-10,05; 1,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 2,64</t>
+          <t>-8,99; 2,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 4,92</t>
+          <t>-7,63; 4,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -0,65</t>
+          <t>-8,94; -0,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 1,34</t>
+          <t>-7,52; 1,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 0,97</t>
+          <t>-7,61; 1,24</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 267,75</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 248,73</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 385,18</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 377,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,1</t>
+          <t>-100,0; 20,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,74; 66,11</t>
+          <t>-90,43; 70,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-92,67; 53,76</t>
+          <t>-90,42; 71,02</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; -0,27</t>
+          <t>-4,78; -0,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,42</t>
+          <t>-4,22; 0,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 20,96</t>
+          <t>-3,79; 24,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,2</t>
+          <t>-3,3; 0,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,78</t>
+          <t>-4,1; -0,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; -1,18</t>
+          <t>-4,3; -1,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,49</t>
+          <t>-3,23; -0,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,79</t>
+          <t>-3,48; -0,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,96</t>
+          <t>-3,3; 9,14</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-60,68%</t>
+          <t>-60,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-41,57%</t>
+          <t>-41,16%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-76,58%</t>
+          <t>-76,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-54,02%</t>
+          <t>-53,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-57,37%</t>
+          <t>-57,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,1; -3,57</t>
+          <t>-85,66; 0,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,77; 21,39</t>
+          <t>-75,18; 16,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,75; 777,96</t>
+          <t>-88,04; 874,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,34; 20,01</t>
+          <t>-78,68; 26,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-94,38; -26,54</t>
+          <t>-94,31; -23,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-96,53; -46,33</t>
+          <t>-96,24; -50,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,53; -15,91</t>
+          <t>-77,44; -17,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,24; -26,23</t>
+          <t>-77,15; -19,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-88,15; 286,09</t>
+          <t>-87,98; 397,61</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-0,92</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 5,02</t>
+          <t>-2,76; 4,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; -0,95</t>
+          <t>-5,77; -1,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; -0,25</t>
+          <t>-5,39; -0,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,41</t>
+          <t>-3,57; 1,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,31</t>
+          <t>-3,02; 2,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,72</t>
+          <t>-2,37; 3,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,93</t>
+          <t>-2,41; 2,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,14</t>
+          <t>-3,56; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,23</t>
+          <t>-2,8; 1,17</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-84,24%</t>
+          <t>-84,16%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-45,61%</t>
+          <t>-45,02%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>-3,79%</t>
+          <t>-2,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-29,09%</t>
+          <t>-28,58%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,3; 470,05</t>
+          <t>-71,32; 488,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 465,18</t>
+          <t>-100,0; 495,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,69; 580,58</t>
+          <t>-81,15; 509,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,23; 163,46</t>
+          <t>-70,27; 171,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,08</t>
+          <t>-100,0; 42,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,53; 106,3</t>
+          <t>-79,32; 116,63</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,12</t>
+          <t>-3,47; -0,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,43</t>
+          <t>-3,73; -0,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 14,78</t>
+          <t>-3,64; 12,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,01</t>
+          <t>-2,95; -0,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,54</t>
+          <t>-3,24; -0,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; -0,42</t>
+          <t>-3,22; -0,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,65</t>
+          <t>-2,87; -0,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,95</t>
+          <t>-3,13; -0,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 5,71</t>
+          <t>-2,77; 5,26</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-47,24%</t>
+          <t>-47,1%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-53,49%</t>
+          <t>-53,28%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-48,55%</t>
+          <t>-48,41%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-63,38%</t>
+          <t>-63,33%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-57,55%</t>
+          <t>-57,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-48,08%</t>
+          <t>-47,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-58,14%</t>
+          <t>-58,02%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-15,69%</t>
+          <t>-15,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -0,95</t>
+          <t>-72,84; -1,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,0; -14,11</t>
+          <t>-75,13; -14,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,54; 488,8</t>
+          <t>-87,84; 502,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-75,32; 4,31</t>
+          <t>-75,89; -0,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,44; -16,93</t>
+          <t>-82,83; -22,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,09; -16,51</t>
+          <t>-79,43; -11,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-69,89; -21,84</t>
+          <t>-70,72; -19,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,46; -31,68</t>
+          <t>-75,54; -33,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,88; 206,62</t>
+          <t>-75,83; 180,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 0,12</t>
+          <t>-11,2; 0,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 3,91</t>
+          <t>-9,34; 3,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 1,23</t>
+          <t>-10,44; 1,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 1,73</t>
+          <t>-9,97; 1,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 2,6</t>
+          <t>-9,21; 2,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 4,74</t>
+          <t>-7,95; 4,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -0,02</t>
+          <t>-8,83; -0,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 1,11</t>
+          <t>-7,23; 1,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 1,24</t>
+          <t>-7,62; 1,42</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 267,75</t>
+          <t>-100,0; 277,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 248,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 377,77</t>
+          <t>-100,0; 501,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 20,92</t>
+          <t>-100,0; 9,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-90,43; 70,18</t>
+          <t>-89,58; 66,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-90,42; 71,02</t>
+          <t>-89,69; 84,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -0,27</t>
+          <t>-4,73; -0,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,34</t>
+          <t>-3,78; 0,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 24,2</t>
+          <t>-3,8; 20,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,34</t>
+          <t>-3,35; 0,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -0,8</t>
+          <t>-4,12; -0,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; -1,14</t>
+          <t>-4,33; -1,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,66</t>
+          <t>-3,35; -0,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -0,65</t>
+          <t>-3,44; -0,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 9,14</t>
+          <t>-3,25; 11,62</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,66; 0,84</t>
+          <t>-85,16; 0,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,18; 16,47</t>
+          <t>-71,33; 25,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,04; 874,63</t>
+          <t>-89,49; 797,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-78,68; 26,2</t>
+          <t>-80,83; 24,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-94,31; -23,68</t>
+          <t>-94,65; -32,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-96,24; -50,18</t>
+          <t>-95,31; -41,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,44; -17,49</t>
+          <t>-75,67; -19,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,15; -19,75</t>
+          <t>-77,58; -25,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,98; 397,61</t>
+          <t>-86,65; 491,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 4,56</t>
+          <t>-2,71; 4,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; -1,01</t>
+          <t>-5,78; -0,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,39; -0,33</t>
+          <t>-5,5; -0,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,49</t>
+          <t>-3,45; 1,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,26</t>
+          <t>-3,44; 2,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,67</t>
+          <t>-2,31; 3,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,14</t>
+          <t>-2,17; 2,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,0</t>
+          <t>-3,59; 0,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,17</t>
+          <t>-2,78; 1,34</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 488,86</t>
+          <t>-71,39; 517,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 495,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,15; 509,8</t>
+          <t>-74,4; 521,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,27; 171,21</t>
+          <t>-68,59; 192,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,12</t>
+          <t>-100,0; 25,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-79,32; 116,63</t>
+          <t>-78,48; 142,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,09</t>
+          <t>-3,46; -0,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,54</t>
+          <t>-3,57; -0,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 12,91</t>
+          <t>-3,56; 14,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,1</t>
+          <t>-2,91; -0,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,59</t>
+          <t>-3,21; -0,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,36</t>
+          <t>-3,05; -0,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,58</t>
+          <t>-2,78; -0,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -0,97</t>
+          <t>-3,04; -0,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 5,26</t>
+          <t>-2,81; 7,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-72,84; -1,56</t>
+          <t>-74,47; -4,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,13; -14,4</t>
+          <t>-73,98; -10,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-87,84; 502,31</t>
+          <t>-86,87; 427,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-75,89; -0,24</t>
+          <t>-75,69; 2,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,83; -22,11</t>
+          <t>-83,15; -20,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,43; -11,62</t>
+          <t>-77,36; -13,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-70,72; -19,61</t>
+          <t>-68,26; -14,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,54; -33,51</t>
+          <t>-73,63; -29,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,83; 180,52</t>
+          <t>-75,91; 265,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,02</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,49</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-4,7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,93</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,02</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,56</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>-4,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-2,73</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 0,39</t>
+          <t>-10,08; 1,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 3,72</t>
+          <t>-8,89; 2,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 1,97</t>
+          <t>-7,73; 4,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 1,68</t>
+          <t>-12,36; 0,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 2,59</t>
+          <t>-8,77; 3,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 4,64</t>
+          <t>-10,98; 2,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -0,55</t>
+          <t>-8,35; -0,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 1,4</t>
+          <t>-7,45; 1,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,42</t>
+          <t>-7,41; 1,47</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-59,73%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-50,61%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-29,52%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-78,95%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-49,23%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-74,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-59,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-50,61%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-29,87%</t>
+          <t>-68,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-53,0%</t>
+          <t>-49,42%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 277,1</t>
+          <t>-100,0; 385,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 501,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 9,4</t>
+          <t>-100,0; 18,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-89,58; 66,15</t>
+          <t>-88,74; 66,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,69; 84,26</t>
+          <t>-91,7; 73,85</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,34</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-2,56</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,64</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,49</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,34</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>-2,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-2,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -0,3</t>
+          <t>-3,36; 0,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,43</t>
+          <t>-4,17; -0,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 20,38</t>
+          <t>-4,37; -1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,32</t>
+          <t>-4,53; -0,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; -0,85</t>
+          <t>-3,82; 0,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -1,2</t>
+          <t>-4,92; -0,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,58</t>
+          <t>-3,36; -0,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,75</t>
+          <t>-3,36; -0,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 11,62</t>
+          <t>-4,01; -1,39</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-46,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-76,54%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-83,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-60,61%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-41,16%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62,42%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-46,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-76,54%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-83,14%</t>
+          <t>-66,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-4,75%</t>
+          <t>-74,39%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,16; 0,54</t>
+          <t>-79,34; 20,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,33; 25,71</t>
+          <t>-94,65; -29,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,49; 797,48</t>
+          <t>-96,6; -45,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-80,83; 24,87</t>
+          <t>-84,9; -0,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-94,65; -32,56</t>
+          <t>-70,7; 30,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-95,31; -41,04</t>
+          <t>-89,58; 19,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,67; -19,89</t>
+          <t>-77,88; -20,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,58; -25,03</t>
+          <t>-76,4; -19,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 491,0</t>
+          <t>-88,63; -31,36</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,39</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,88</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,59</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>-2,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-0,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,61</t>
+          <t>-3,58; 1,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,78; -0,9</t>
+          <t>-3,42; 2,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; -0,18</t>
+          <t>-1,97; 4,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,65</t>
+          <t>-2,06; 5,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,26</t>
+          <t>-5,61; -0,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,44</t>
+          <t>-4,95; -0,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,29</t>
+          <t>-2,41; 2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,01</t>
+          <t>-3,35; 0,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,34</t>
+          <t>-2,58; 1,29</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-45,02%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-19,22%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>43,41%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>38,5%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-84,16%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-45,02%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-19,22%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>-83,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-28,58%</t>
+          <t>-25,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,39; 517,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 465,18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-73,91; 602,72</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-67,8; 496,34</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-74,4; 521,55</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,59; 192,26</t>
+          <t>-70,85; 145,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 25,91</t>
+          <t>-100,0; 56,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,48; 142,64</t>
+          <t>-76,14; 114,02</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,04</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-2,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,18</t>
+          <t>-3,08; 0,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,4</t>
+          <t>-3,36; -0,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 14,25</t>
+          <t>-3,19; -0,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,17</t>
+          <t>-3,67; -0,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,59</t>
+          <t>-3,75; -0,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,37</t>
+          <t>-4,35; -0,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,54</t>
+          <t>-2,77; -0,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,89</t>
+          <t>-3,07; -1,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 7,0</t>
+          <t>-3,28; -1,08</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-48,41%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-63,33%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-56,03%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-47,1%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-53,28%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>23,03%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-48,41%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-63,33%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-57,46%</t>
+          <t>-69,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-15,55%</t>
+          <t>-63,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-74,47; -4,28</t>
+          <t>-76,73; 2,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,98; -10,43</t>
+          <t>-83,75; -24,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,87; 427,37</t>
+          <t>-79,71; -9,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-75,69; 2,51</t>
+          <t>-73,27; 4,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,15; -20,15</t>
+          <t>-75,39; -9,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,36; -13,2</t>
+          <t>-88,3; -16,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,26; -14,79</t>
+          <t>-67,48; -17,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,63; -29,8</t>
+          <t>-75,65; -31,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,91; 265,15</t>
+          <t>-79,38; -33,23</t>
         </is>
       </c>
     </row>
